--- a/output/full_scan/batch_seq8_2026-08-31.xlsx
+++ b/output/full_scan/batch_seq8_2026-08-31.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>934.6464191331688</v>
+        <v>1134.646419133169</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>166</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>76.04867302442531</v>
+        <v>76.04867301461461</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26.93209350312853</v>
+        <v>26.93209358306256</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.064641913316895</v>
@@ -570,51 +570,51 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.66947327835148</v>
+        <v>1.669473278828476</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6949</v>
+        <v>6933</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>903.850713129944</v>
+        <v>1074.848422769723</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1490</v>
+        <v>286</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>84.44665559436557</v>
+        <v>83.7055583849419</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>38.63673919390333</v>
+        <v>28.79934723729491</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.896361293282596</v>
+        <v>2.584842276972337</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>44.09810044583309</v>
+        <v>8.837106595320705</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6933</v>
+        <v>7788</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>769.8484227697234</v>
+        <v>946.3434720320012</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>83.70555835854941</v>
+        <v>68.15329604699762</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>28.79934723651438</v>
+        <v>29.33031348575344</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.584842276972337</v>
+        <v>2.604152504716576</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>8.837106595893083</v>
+        <v>6.776225122568871</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7810</v>
+        <v>7711</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>742.6082732718419</v>
+        <v>903.9202941904668</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>226</v>
+        <v>535</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>72.90555846085363</v>
+        <v>72.30310030817176</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31.91201629807608</v>
+        <v>44.87096799771573</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.360827327184185</v>
+        <v>1.430066939830752</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,51 +729,51 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.227779720493597</v>
+        <v>3.140201911347688</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7744</v>
+        <v>6949</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>708.0114575972616</v>
+        <v>893.8507131299439</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>503</v>
+        <v>1490</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.98602510818843</v>
+        <v>84.44665560156646</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>31.24541547671731</v>
+        <v>38.636739280408</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.8976613379003019</v>
+        <v>1.896361293282596</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.584762860534889</v>
+        <v>44.09810044523214</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6922</v>
+        <v>7810</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>670.737288283382</v>
+        <v>882.6082732718419</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>57.91416285772633</v>
+        <v>72.90555848638739</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.46480299683866</v>
+        <v>31.91201627382071</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5354773040598869</v>
+        <v>3.360827327184185</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.3412730092292033</v>
+        <v>3.227779720264629</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7711</v>
+        <v>7744</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>653.9202941904667</v>
+        <v>823.0114575972616</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>535</v>
+        <v>503</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>72.30310026208036</v>
+        <v>58.98602514880613</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>44.87096799147648</v>
+        <v>31.24541560527702</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.430066939830752</v>
+        <v>0.8976613379003019</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3.140201912397004</v>
+        <v>2.584762859676317</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7788</v>
+        <v>6895</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>636.3434720320013</v>
+        <v>804.4873143219041</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>316</v>
+        <v>163.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.15329600818086</v>
+        <v>79.67005287833186</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>29.33031337076398</v>
+        <v>25.87431919889056</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.604152504716576</v>
+        <v>4.819240187425331</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>6.776225123713587</v>
+        <v>4.871942932852118</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7792</v>
+        <v>8039</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>622.9303427490867</v>
+        <v>728.9185419577017</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>71.58640372932729</v>
+        <v>66.08270894595164</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46.44037479360803</v>
+        <v>38.66640329085472</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5132459544299049</v>
+        <v>1.051942894210639</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>5.183568786610333</v>
+        <v>6.331671881291616</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7795</v>
+        <v>6894</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>607.0757168320614</v>
+        <v>722.8625725883145</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>508</v>
+        <v>354</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>49.54358209278251</v>
+        <v>59.56369563216909</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.43102282125575</v>
+        <v>11.79477822930434</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9725536823945836</v>
+        <v>4.129745226815234</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.1859998058484713</v>
+        <v>2.155422773354102</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6895</v>
+        <v>6840</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>604.4873143219025</v>
+        <v>712.3392604741496</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>163.5</v>
+        <v>94</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>79.67005295584006</v>
+        <v>75.64192758598858</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25.87431919211354</v>
+        <v>39.67728455657824</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4.819240187425331</v>
+        <v>0.7136522515787941</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>1</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>4.871942930944165</v>
+        <v>1.754236873043629</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7751</v>
+        <v>6922</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>599.4702364544096</v>
+        <v>670.737288283382</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1615</v>
+        <v>207</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>53.39240146966848</v>
+        <v>57.91416292223247</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>21.66332050974458</v>
+        <v>26.46480298486544</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.363122326114411</v>
+        <v>0.5354773040598869</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>27.14276659054387</v>
+        <v>0.3412730090384475</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6952</v>
+        <v>6918</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>583.6766108261589</v>
+        <v>669.4009029218633</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>38.2</v>
+        <v>77.2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>59.00147094685984</v>
+        <v>64.86097505545146</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>17.94541916751855</v>
+        <v>35.10509476840005</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.547678911424286</v>
+        <v>0.7366447985004686</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0004521453849249</v>
+        <v>0.4750296056914083</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6894</v>
+        <v>6885</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>582.8625725883145</v>
+        <v>625.6578169415642</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>354</v>
+        <v>23.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.56369561141492</v>
+        <v>69.53519132721389</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>11.79477815054821</v>
+        <v>26.66487862234906</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.129745226815234</v>
+        <v>1.037647425219437</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.155422773354102</v>
+        <v>0.3202539319135286</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6859</v>
+        <v>7792</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>570.8722994604241</v>
+        <v>622.9303427490867</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>111</v>
+        <v>301</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.73758044687755</v>
+        <v>71.58640373645113</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.88879457545002</v>
+        <v>46.44037483227518</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.977212658343396</v>
+        <v>0.5132459544299049</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.827404354952741</v>
+        <v>5.18356878651495</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6918</v>
+        <v>7795</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>554.4009029218628</v>
+        <v>607.0757168320614</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>77.2</v>
+        <v>508</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.86097543069079</v>
+        <v>49.54358209377332</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>35.1050947218543</v>
+        <v>25.43102282125575</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7366447985004686</v>
+        <v>0.9725536823945836</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.4750296039361096</v>
+        <v>-0.1859998060391987</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6969</v>
+        <v>6906</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>534.792903985568</v>
+        <v>605.5233496067671</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>34.6</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.80772815725314</v>
+        <v>58.67422156904922</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.03946019415209</v>
+        <v>21.72691315832148</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3847102409695759</v>
+        <v>2.2603418566288</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.1145304455178948</v>
+        <v>1.166253594356497</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7714</v>
+        <v>7751</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>525.3560253720335</v>
+        <v>599.4702364544096</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>169</v>
+        <v>1615</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.39443420016548</v>
+        <v>53.39240147942858</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.4529250610239</v>
+        <v>21.66332049772722</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4850679511527963</v>
+        <v>2.363122326114411</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.690324833272939</v>
+        <v>27.14276658958993</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6840</v>
+        <v>8021</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>512.3392604741495</v>
+        <v>588.0703526102153</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>94</v>
+        <v>435</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>75.64192760515151</v>
+        <v>53.28164589486582</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>39.67728452819565</v>
+        <v>11.59623402422289</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7136522515787941</v>
+        <v>1.57740414891753</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.754236872776514</v>
+        <v>6.325153612668283</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7556</v>
+        <v>6952</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>486.5932750608141</v>
+        <v>583.6766108261586</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>248.5</v>
+        <v>38.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.91624261462884</v>
+        <v>59.0014708233547</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.67660446551794</v>
+        <v>17.9454192016005</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9986324305670941</v>
+        <v>1.547678911424286</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.551523046907719</v>
+        <v>0.0004521453563049</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6854</v>
+        <v>7828</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>480.9653035649927</v>
+        <v>583.2935040766449</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>93.2</v>
+        <v>1765</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45.43418435444021</v>
+        <v>53.93107801063987</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26.03478076116561</v>
+        <v>11.90961279531661</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.051068056537973</v>
+        <v>2.465711112729657</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.035690172539512</v>
+        <v>19.78567990154608</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7631</v>
+        <v>7728</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>469.9381659842055</v>
+        <v>580.550510999833</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>144</v>
+        <v>632</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.48001792999402</v>
+        <v>56.55821244417216</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.96273030427421</v>
+        <v>20.27802367802788</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.25915333284632</v>
+        <v>0.9482394663514312</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2240075765502112</v>
+        <v>8.548832898766539</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6885</v>
+        <v>6859</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>455.6578169415642</v>
+        <v>570.8722994604241</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>23.1</v>
+        <v>111</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>69.53519115863433</v>
+        <v>56.73758072463068</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.6648786549287</v>
+        <v>20.88879463851892</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.037647425219437</v>
+        <v>1.977212658343396</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3202539321138623</v>
+        <v>0.8274043535217761</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6962</v>
+        <v>7402</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>445.1437304253251</v>
+        <v>558.5252353929228</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>31.55</v>
+        <v>109.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46.77699086521694</v>
+        <v>49.85108466122079</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>18.24126401342032</v>
+        <v>20.44153474829368</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.848243140143993</v>
+        <v>0.489973876585192</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1452135741148869</v>
+        <v>0.6722371446309138</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8039</v>
+        <v>6937</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>443.9185419577016</v>
+        <v>552.2059319409631</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>66.08270894236659</v>
+        <v>54.53711646969575</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>38.66640316779964</v>
+        <v>9.543884880573495</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.051942894210639</v>
+        <v>0.8192148220244354</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>6.331671881387003</v>
+        <v>1.8174951114712</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7402</v>
+        <v>6969</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>443.5252353929228</v>
+        <v>544.792903985568</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>109.5</v>
+        <v>34.6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.85108469603677</v>
+        <v>55.80772813646959</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.44153474010877</v>
+        <v>21.03946021276007</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.489973876585192</v>
+        <v>0.3847102409695759</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6722371443637998</v>
+        <v>-0.1145304454415763</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6931</v>
+        <v>7714</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>438.5880375149209</v>
+        <v>525.3560253720335</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>41.45</v>
+        <v>169</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>57.16646805181853</v>
+        <v>51.39443412006818</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>28.13365658566881</v>
+        <v>25.45292513599192</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5433904933130207</v>
+        <v>0.4850679511527963</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.047627759214605</v>
+        <v>0.6903248342268933</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6906</v>
+        <v>6953</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>435.5233496067671</v>
+        <v>498.5835986759196</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>58.6742215237052</v>
+        <v>56.69620746741212</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.72691315832149</v>
+        <v>17.87662982837557</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.2603418566288</v>
+        <v>1.101132466507118</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.166253594547297</v>
+        <v>1.776178802457025</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8021</v>
+        <v>7750</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>433.0703526102141</v>
+        <v>492.524395833309</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>435</v>
+        <v>2270</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.28164588942992</v>
+        <v>49.14102612306484</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11.59623402422289</v>
+        <v>15.16969302488914</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.57740414891753</v>
+        <v>0.4095906513585368</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>6.325153612448855</v>
+        <v>-17.36270998841214</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6936</v>
+        <v>6983</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>428.9263995862728</v>
+        <v>487.7455695877966</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>32.35</v>
+        <v>348</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>50.45159551813521</v>
+        <v>63.89480547945443</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30.74753820071486</v>
+        <v>15.27387471609868</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7605706558896368</v>
+        <v>1.374556958779662</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.049686208930025</v>
+        <v>7.924144651633132</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7712</v>
+        <v>7556</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>423.7568750952885</v>
+        <v>486.5932750608142</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>152.5</v>
+        <v>248.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.37405598697871</v>
+        <v>53.91624263098847</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>17.43070882373674</v>
+        <v>28.67660444493436</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.005391845997046</v>
+        <v>0.9986324305670941</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.387084529108694</v>
+        <v>2.551523047003133</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6902</v>
+        <v>6854</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>423.7253381125238</v>
+        <v>480.9653035649927</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>127.5</v>
+        <v>93.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>50.799139344035</v>
+        <v>45.4341843432637</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13.07545925497285</v>
+        <v>26.03478077325768</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7688788957384376</v>
+        <v>2.051068056537973</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0142112476878474</v>
+        <v>1.035690172444115</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7738</v>
+        <v>7717</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>423.1334948296384</v>
+        <v>473.2506259683814</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>169</v>
+        <v>427</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>52.03533781550045</v>
+        <v>50.69366902791133</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>32.66061669341574</v>
+        <v>14.77696967324033</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4335485993994488</v>
+        <v>2.045278743473069</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.3217371227415989</v>
+        <v>5.350553439289296</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6887</v>
+        <v>7631</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>421.6205721563111</v>
+        <v>469.9381659842055</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>36.55</v>
+        <v>144</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>48.26913842872022</v>
+        <v>52.48001790677055</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.06547965535585</v>
+        <v>22.96273025742916</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9120533537688454</v>
+        <v>0.25915333284632</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.1067568595417838</v>
+        <v>0.2240075765502112</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6855</v>
+        <v>6944</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>415.5637281131571</v>
+        <v>449.5170075471022</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116</v>
+        <v>717</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.5032550873606</v>
+        <v>39.60487334089494</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10.89030904764402</v>
+        <v>26.5507278781273</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9414225941422594</v>
+        <v>0.8312266757980494</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>3.151863392355128</v>
+        <v>5.624735418631552</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7728</v>
+        <v>6962</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>410.5505109998331</v>
+        <v>445.1437304253251</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>632</v>
+        <v>31.55</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.55821241772992</v>
+        <v>46.77699106411367</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.27802362610888</v>
+        <v>18.24126397060668</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9482394663514312</v>
+        <v>2.848243140143993</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>8.548832899720468</v>
+        <v>0.1452135740004166</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6907</v>
+        <v>6931</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>405.1857380821716</v>
+        <v>438.5880375149209</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>184</v>
+        <v>41.45</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.15213307043075</v>
+        <v>57.16646812487017</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15.80250050534019</v>
+        <v>28.13365663796078</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3609585563555844</v>
+        <v>0.5433904933130207</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0899784144879833</v>
+        <v>0.0476277590238071</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7749</v>
+        <v>7799</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>401.3151080922826</v>
+        <v>438.21291054998</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>362</v>
+        <v>367.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.59240599227597</v>
+        <v>49.57801760350572</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.3861310789795</v>
+        <v>15.54957363082958</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.452211063197097</v>
+        <v>0.9853951207844552</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>5.237673718361472</v>
+        <v>3.188651862977228</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7689</v>
+        <v>8042</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>398.2129019534463</v>
+        <v>431.6552080906645</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>174.5</v>
+        <v>105</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>37.86169176450834</v>
+        <v>44.28614726829567</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.12965467973799</v>
+        <v>19.81569517322998</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6170539325868675</v>
+        <v>1.066385853878294</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.654495225423968</v>
+        <v>1.586742263241865</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6928</v>
+        <v>6936</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>385.4015561465688</v>
+        <v>428.9263995862725</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>47.8</v>
+        <v>32.35</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.34040864031313</v>
+        <v>50.45159550813071</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12.6454760045496</v>
+        <v>30.74753821195397</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4523162781625073</v>
+        <v>0.7605706558896368</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0433073776360517</v>
+        <v>0.0496862089586495</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6944</v>
+        <v>7712</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>384.5170075471022</v>
+        <v>423.7568750952885</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>717</v>
+        <v>152.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>39.60487332230921</v>
+        <v>52.37405598697871</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>26.5507278669413</v>
+        <v>17.43070877610395</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8312266757980494</v>
+        <v>1.005391845997046</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>5.624735418440721</v>
+        <v>2.387084529108694</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6953</v>
+        <v>6902</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>383.5835986759196</v>
+        <v>423.7253381125238</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>234</v>
+        <v>127.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>56.69620731840424</v>
+        <v>50.79913944659302</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>17.87662974979198</v>
+        <v>13.07545926799737</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.101132466507118</v>
+        <v>0.7688788957384376</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.776178803792595</v>
+        <v>-0.0142112478404882</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7828</v>
+        <v>7738</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>383.2935040766449</v>
+        <v>423.1334948296382</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1765</v>
+        <v>169</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.93107799748657</v>
+        <v>52.03533721281034</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11.90961273928084</v>
+        <v>32.66061676231788</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.465711112729657</v>
+        <v>0.4335485993994488</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>19.78567990269092</v>
+        <v>0.3217371267482776</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7842</v>
+        <v>6887</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>382.9637669615636</v>
+        <v>421.620572156311</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>36.55</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.85559994614784</v>
+        <v>48.26913833548912</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.63203720374447</v>
+        <v>26.06547956481894</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2637164133514498</v>
+        <v>0.9120533537688454</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.9764225415813296</v>
+        <v>0.1067568595227019</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6937</v>
+        <v>7689</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>382.2059319409629</v>
+        <v>418.2129019534463</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>282</v>
+        <v>174.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.53711644127192</v>
+        <v>37.86169176450834</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9.543884862540706</v>
+        <v>22.12965467973799</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8192148220244354</v>
+        <v>0.6170539325868675</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.81749511223435</v>
+        <v>2.654495225423968</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7730</v>
+        <v>6855</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>379.5907032091581</v>
+        <v>415.5637281131571</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.13584289766951</v>
+        <v>52.50325509260748</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.73272173068293</v>
+        <v>10.89030904855401</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.488080337981943</v>
+        <v>0.9414225941422594</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.896089797314432</v>
+        <v>3.151863391973539</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7704</v>
+        <v>6907</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>379.5185915286084</v>
+        <v>405.1857380821716</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>62.6</v>
+        <v>184</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.89149712441802</v>
+        <v>50.15213307043075</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.79516048452993</v>
+        <v>15.80250050534019</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2202316925481872</v>
+        <v>0.3609585563555844</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.1920116210919706</v>
+        <v>-0.0899784144879833</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7769</v>
+        <v>8034</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>374.4318458694318</v>
+        <v>404.0327591979818</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>5860</v>
+        <v>19.75</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40.09624188734575</v>
+        <v>54.65935354956309</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>8.383331060961595</v>
+        <v>33.37979837279559</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.634219468161909</v>
+        <v>0.7059588992237673</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-33.93498319019187</v>
+        <v>0.2579992159014022</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6870</v>
+        <v>7768</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>373.1873193979085</v>
+        <v>391.5114955189864</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>252</v>
+        <v>291.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.89192864781308</v>
+        <v>52.02711522522733</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8.17734166538067</v>
+        <v>25.0034516486362</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5091087207992845</v>
+        <v>0.7419431295284338</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0079156952266425</v>
+        <v>4.237003183623627</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7715</v>
+        <v>7749</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>372.8971034178871</v>
+        <v>391.3151080922826</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>29.6</v>
+        <v>362</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>39.0878178986683</v>
+        <v>49.59240574417654</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.97030853014788</v>
+        <v>20.38613110815376</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.103873842424881</v>
+        <v>5.452211063197097</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.2878946200899275</v>
+        <v>5.23767372294054</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6934</v>
+        <v>6928</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>371.810081020299</v>
+        <v>385.4015561465689</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>74.3</v>
+        <v>47.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.38273423201165</v>
+        <v>46.34040892341772</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.19800935421228</v>
+        <v>12.64547619040725</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.650209865769023</v>
+        <v>0.4523162781625073</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1978809983548865</v>
+        <v>0.0433073773784828</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7768</v>
+        <v>7842</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>371.5114955189863</v>
+        <v>382.9637669615635</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>291.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.02711519348833</v>
+        <v>53.85560020515761</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>25.00345159607032</v>
+        <v>17.63203720374447</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7419431295284338</v>
+        <v>0.2637164133514498</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>4.237003183909834</v>
+        <v>0.9764225394825972</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6957</v>
+        <v>7704</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>362.5155178689084</v>
+        <v>379.5185915286084</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>219.5</v>
+        <v>62.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.30089237140408</v>
+        <v>54.89149735217495</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.28203628301196</v>
+        <v>18.79516050230333</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.151175913107706</v>
+        <v>0.2202316925481872</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.655461077872517</v>
+        <v>-0.1920116215689571</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7822</v>
+        <v>7769</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>361.4536801364437</v>
+        <v>374.5862657524254</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>914</v>
+        <v>5860</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.43300986495267</v>
+        <v>40.09624190238655</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.4723292228876</v>
+        <v>8.383330951595566</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8671666231326882</v>
+        <v>2.66147441805838</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>11.25859308861665</v>
+        <v>-33.93498318923803</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6947</v>
+        <v>6870</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>359.3076092686366</v>
+        <v>373.1873193979085</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>70.3</v>
+        <v>252</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>38.26309306748687</v>
+        <v>43.89192867359345</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.99663812241943</v>
+        <v>8.17734166538067</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7619383676668425</v>
+        <v>0.5091087207992845</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0481279018240545</v>
+        <v>0.0079156952266425</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6996</v>
+        <v>7715</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>356.662127647589</v>
+        <v>372.8971034178871</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>177.5</v>
+        <v>29.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>47.42657806373693</v>
+        <v>39.08781787936584</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.88526385667662</v>
+        <v>17.970308526234</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3913983851317691</v>
+        <v>3.103873842424881</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.4043617586110787</v>
+        <v>-0.2878946200803901</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6861</v>
+        <v>6934</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>353.1751883249678</v>
+        <v>371.810081020299</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>188</v>
+        <v>74.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>36.6380161226894</v>
+        <v>52.38273444010746</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.64791796434395</v>
+        <v>13.19800933560684</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7531277713278542</v>
+        <v>1.650209865769023</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>1.916462747552924</v>
+        <v>0.1978809978397447</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8028</v>
+        <v>7730</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>352.5895938692098</v>
+        <v>369.5907032091581</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>39.05911646543896</v>
+        <v>52.13584289766951</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.87618215346838</v>
+        <v>16.73272173068293</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.352066921276425</v>
+        <v>0.488080337981943</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.5821213316398861</v>
+        <v>1.896089796742037</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7750</v>
+        <v>6957</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>352.524395833309</v>
+        <v>362.5155178689084</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2270</v>
+        <v>219.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.14102612193816</v>
+        <v>51.30089242692677</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.16969301479595</v>
+        <v>14.28203635528072</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4095906513585368</v>
+        <v>2.151175913107706</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-17.36270998955716</v>
+        <v>0.6554610772047449</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6924</v>
+        <v>7822</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>350.599677362501</v>
+        <v>361.4536801364437</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>112</v>
+        <v>914</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>48.09824518295802</v>
+        <v>50.43300990992924</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>17.37084782422599</v>
+        <v>13.4723293303907</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5192490796796317</v>
+        <v>0.8671666231326882</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2672964297964689</v>
+        <v>11.25859308842583</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8016</v>
+        <v>6947</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>349.3459850397196</v>
+        <v>359.3076092686366</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>289</v>
+        <v>70.3</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.29454338299907</v>
+        <v>38.26309307368661</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10.4546300134396</v>
+        <v>13.99663812255344</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.54135840081251</v>
+        <v>0.7619383676668425</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.4767541832095586</v>
+        <v>0.0481279017286517</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8040</v>
+        <v>6996</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>347.6422034237491</v>
+        <v>356.6621276475888</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>177.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>39.41300363691918</v>
+        <v>47.42657807272221</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.87324120452261</v>
+        <v>13.88526391156705</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.355432475910685</v>
+        <v>0.3913983851317691</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.5850659873445383</v>
+        <v>0.4043617585156706</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6997</v>
+        <v>6865</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>342.5060777992292</v>
+        <v>356.0224372177213</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>68</v>
+        <v>26.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.26043999698727</v>
+        <v>54.33000542510486</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8.213120217672236</v>
+        <v>11.04910082216005</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.667083437526048</v>
+        <v>0.5185339441899208</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>2.866653823476755</v>
+        <v>1.232349671524366</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6951</v>
+        <v>6861</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>341.9193903870797</v>
+        <v>353.1751883249677</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>71.7</v>
+        <v>188</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.17867859865257</v>
+        <v>36.63801612560965</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>24.69498493670628</v>
+        <v>24.64791802088942</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9206010945363228</v>
+        <v>0.7531277713278542</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2023943265638536</v>
+        <v>1.916462747448005</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6967</v>
+        <v>8028</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>341.8862743827679</v>
+        <v>352.5895938692103</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>73</v>
+        <v>241</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>52.48841653176304</v>
+        <v>39.05911649093918</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>8.110050120382176</v>
+        <v>21.87618219494607</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3653690890955194</v>
+        <v>1.352066921276425</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.183301450550842</v>
+        <v>0.5821213317353084</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6903</v>
+        <v>6924</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>340.1916939332964</v>
+        <v>350.599677362501</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>313</v>
+        <v>112</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.1926136961827</v>
+        <v>48.0982452333708</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.76060853457694</v>
+        <v>17.37084781309346</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5216620971267654</v>
+        <v>0.5192490796796317</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>2.23795896903974</v>
+        <v>0.2672964297201584</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6923</v>
+        <v>8016</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>329.6763785413733</v>
+        <v>349.3459850397196</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>289</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.38502656976798</v>
+        <v>45.29454349570931</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7.89938841109685</v>
+        <v>10.45463003025041</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.944133252240416</v>
+        <v>0.54135840081251</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.141686145708461</v>
+        <v>-0.4767541842588694</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8011</v>
+        <v>8040</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>328.0951623629304</v>
+        <v>347.6422034237491</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>15.95</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.99877933428883</v>
+        <v>39.41300369796292</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>28.71992688156507</v>
+        <v>20.87324119798341</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6149091892986162</v>
+        <v>1.355432475910685</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0434162430727232</v>
+        <v>0.5850659872873107</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7703</v>
+        <v>6997</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>328.0731217072325</v>
+        <v>342.5060777992292</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>179</v>
+        <v>68</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>48.17412658949638</v>
+        <v>52.26043999839642</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>9.988651058474106</v>
+        <v>8.213120267015286</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5468065150892851</v>
+        <v>1.667083437526048</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.9963582165706276</v>
+        <v>2.866653823095164</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7805</v>
+        <v>6951</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>327.8199619894582</v>
+        <v>341.9193903870797</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>508</v>
+        <v>71.7</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>26.81001418416804</v>
+        <v>45.17867858711963</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>36.46888701729975</v>
+        <v>24.69498503240996</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3757710351797232</v>
+        <v>0.9206010945363228</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-18.75396359489701</v>
+        <v>0.2023943265256893</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6914</v>
+        <v>6967</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>327.5255615900455</v>
+        <v>341.8862743827678</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>19.69494232786816</v>
+        <v>52.48842030210199</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>26.20747229490592</v>
+        <v>8.110052726083849</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5588275010487488</v>
+        <v>0.3653690890955194</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-3.170397964815219</v>
+        <v>0.1833014408966465</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6908</v>
+        <v>6903</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>326.8590968996565</v>
+        <v>340.1916939332964</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>30.25</v>
+        <v>313</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>32.69925898613663</v>
+        <v>44.19261370430924</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>35.68251648359704</v>
+        <v>16.76060854283376</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6891323823306457</v>
+        <v>0.5216620971267654</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.007967984727736299</v>
+        <v>2.23795896913516</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7799</v>
+        <v>6923</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>323.2129105499799</v>
+        <v>329.6763785413764</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>367.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.57801776021523</v>
+        <v>51.38502644735125</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.54957370339694</v>
+        <v>7.899388480862163</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9853951207844552</v>
+        <v>0.944133252240416</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>3.188651860496894</v>
+        <v>0.1416861461854489</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7721</v>
+        <v>8011</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>308.5130398940559</v>
+        <v>328.0951623629306</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>61.3</v>
+        <v>15.95</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.91065754268582</v>
+        <v>42.99877933428883</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.33959466346691</v>
+        <v>28.71992692906243</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7191273826311189</v>
+        <v>0.6149091892986162</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2838810016637372</v>
+        <v>0.0434162430918025</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7765</v>
+        <v>7703</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>303.5341828248466</v>
+        <v>328.0731217072325</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>223.5</v>
+        <v>179</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.18532184475314</v>
+        <v>48.17412657324027</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.57122903663845</v>
+        <v>9.988651066587192</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8152849589239198</v>
+        <v>0.5468065150892851</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.09706785328500731</v>
+        <v>0.9963582168568434</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7717</v>
+        <v>7805</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>303.2506259683814</v>
+        <v>327.8199619894582</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>427</v>
+        <v>508</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.69366902791133</v>
+        <v>26.81001415734304</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.77696967324033</v>
+        <v>36.46888700574316</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.045278743473069</v>
+        <v>0.3757710351797232</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>5.350553439289296</v>
+        <v>-18.75396359489701</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6921</v>
+        <v>6914</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>299.6162317366853</v>
+        <v>327.5255615900455</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>64.5</v>
+        <v>122</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.52226178704785</v>
+        <v>19.69494235235517</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.40118134174078</v>
+        <v>26.20747234266092</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1450628873291419</v>
+        <v>0.5588275010487488</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.3141170935188924</v>
+        <v>-3.170397965006042</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6916</v>
+        <v>6908</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>296.1388064419273</v>
+        <v>326.8590968996565</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>18.3</v>
+        <v>30.25</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>43.98436779597574</v>
+        <v>32.69926273810761</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10.04593353860677</v>
+        <v>35.68251397723555</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.106016079736043</v>
+        <v>0.6891323823306457</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0095039949727472</v>
+        <v>-0.0079679954122269</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7855</v>
+        <v>7721</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>295.8916948592268</v>
+        <v>308.5130398940559</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>43.1</v>
+        <v>61.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>17.91659101029644</v>
+        <v>43.91065777995818</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46.90527525430768</v>
+        <v>16.33959468834468</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.504203387900246</v>
+        <v>0.7191273826311189</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.7586373248403717</v>
+        <v>0.2838810011867527</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7820</v>
+        <v>7765</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>295.096383346915</v>
+        <v>303.5341828248466</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>122</v>
+        <v>223.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>58.88583035262253</v>
+        <v>46.18532208173232</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.82605575399648</v>
+        <v>22.57122914254692</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.7710314134612606</v>
+        <v>0.8152849589239198</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.5378481538067357</v>
+        <v>0.0970678525218213</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6877</v>
+        <v>6921</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>293.8773709350644</v>
+        <v>299.6162317366853</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>113.5</v>
+        <v>64.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.07229150082244</v>
+        <v>44.52226178704785</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20.31978184072191</v>
+        <v>16.40118134174078</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8916838728271809</v>
+        <v>0.1450628873291419</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.3026905322978561</v>
+        <v>-0.3141170935188924</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8042</v>
+        <v>7610</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>291.6552080906645</v>
+        <v>298.127784064581</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>105</v>
+        <v>1505</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.28614726720907</v>
+        <v>41.50629340953912</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.81569512803042</v>
+        <v>14.18095887611862</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.066385853878294</v>
+        <v>0.8894792868742817</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>1.586742263241865</v>
+        <v>-11.0501554799628</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6955</v>
+        <v>6916</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>290.4900045571119</v>
+        <v>296.1388064419273</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>108</v>
+        <v>18.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>48.9048297062274</v>
+        <v>43.98436795652103</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6.591204834721351</v>
+        <v>10.04593365875508</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5333199719410763</v>
+        <v>1.106016079736043</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.3339204597026319</v>
+        <v>0.009503994867808001</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6983</v>
+        <v>7855</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>287.7455695877966</v>
+        <v>295.8916948592268</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>348</v>
+        <v>43.1</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>63.89480432153882</v>
+        <v>17.91659101029644</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15.27387363102117</v>
+        <v>46.90527525430768</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.374556958779662</v>
+        <v>0.504203387900246</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>7.924144671475785</v>
+        <v>0.7586373248403717</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8033</v>
+        <v>7820</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>282.5817343345874</v>
+        <v>295.096383346915</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>50.14403643863365</v>
+        <v>58.88583047852185</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.73831106020266</v>
+        <v>19.82605579433663</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5549602584913734</v>
+        <v>0.7710314134612606</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.5095450969665289</v>
+        <v>0.5378481535205375</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6919</v>
+        <v>6877</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>281</v>
+        <v>293.8773709350644</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>94.8</v>
+        <v>113.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>37.95217409363989</v>
+        <v>40.07229148790763</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.43912643296708</v>
+        <v>20.31978195423575</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>8.346168235989408</v>
+        <v>0.8916838728271809</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.246441200340397</v>
+        <v>-0.3026905321833908</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6863</v>
+        <v>6955</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>280.6611720715671</v>
+        <v>290.4900045571119</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.04512631475419</v>
+        <v>48.9048289953827</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.71070522479974</v>
+        <v>6.591204860551404</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2555899675456273</v>
+        <v>0.5333199719410763</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.308036670296675</v>
+        <v>-0.3339204240240724</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7734</v>
+        <v>8033</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>279.2457636406494</v>
+        <v>282.5817343345873</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>2825</v>
+        <v>187</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.88375435125499</v>
+        <v>50.14403643071197</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.69222657893114</v>
+        <v>14.73831109820844</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.36770717983554</v>
+        <v>0.5549602584913734</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-22.33641044598485</v>
+        <v>0.5095450971382292</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7610</v>
+        <v>6863</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>278.1277840645813</v>
+        <v>280.6611720715671</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>1505</v>
+        <v>109</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.50629341316673</v>
+        <v>43.04512632678708</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.18095883540384</v>
+        <v>18.71070522479975</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8894792868742817</v>
+        <v>0.2555899675456273</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-11.05015548000075</v>
+        <v>-1.308036670296675</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6901</v>
+        <v>7803</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>270.7736876967443</v>
+        <v>279.3676897429345</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>15.85</v>
+        <v>19.1</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.14193282854517</v>
+        <v>37.98081007351704</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10.37583241958764</v>
+        <v>13.09891052745126</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7690714310596836</v>
+        <v>0.7180005300119253</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.06651491117419379</v>
+        <v>0.07286087913907011</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8034</v>
+        <v>7734</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>264.0327591979818</v>
+        <v>279.2457636406494</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>19.75</v>
+        <v>2825</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>54.65935359596247</v>
+        <v>42.88375437500829</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>33.37979839862064</v>
+        <v>15.69222653932531</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7059588992237673</v>
+        <v>1.36770717983554</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.2579992158441646</v>
+        <v>-22.33641044598485</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8024</v>
+        <v>6901</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>263.5372592168742</v>
+        <v>270.7736876967443</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>13.15</v>
+        <v>15.85</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>38.00026710820143</v>
+        <v>42.14193284164534</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.94358962034018</v>
+        <v>10.37583246344196</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4620710530265068</v>
+        <v>0.7690714310596836</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0005028264611372999</v>
+        <v>-0.0665149112409726</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6971</v>
+        <v>7827</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>261.4283789900721</v>
+        <v>266.9967970554802</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>26.05</v>
+        <v>154.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.26265822823717</v>
+        <v>46.10615730889404</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.53075395037905</v>
+        <v>10.85933925033056</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.134766039366676</v>
+        <v>0.847451512662071</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1104299409207298</v>
+        <v>0.028620582053906</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6994</v>
+        <v>6919</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>257.8591544354101</v>
+        <v>266</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>35.3</v>
+        <v>94.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.48650651712041</v>
+        <v>37.95217494593062</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>29.93073683393271</v>
+        <v>15.43912796794135</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8638746602072428</v>
+        <v>8.835340401994207</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.4047730273828003</v>
+        <v>-1.246441221365868</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7780</v>
+        <v>8024</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>256.7290493113802</v>
+        <v>263.5372592168742</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>16.75</v>
+        <v>13.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.77219187683399</v>
+        <v>38.00026693712866</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>21.53860206554404</v>
+        <v>12.94358971665582</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9126483839864302</v>
+        <v>0.4620710530265068</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0573278203060184</v>
+        <v>-0.0005028264229773</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7818</v>
+        <v>6971</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>255.1513016246124</v>
+        <v>261.4283789900721</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>60.2</v>
+        <v>26.05</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>28.75895222955181</v>
+        <v>47.26265837533147</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.99956127588788</v>
+        <v>16.53075413654874</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.117096110931922</v>
+        <v>1.134766039366676</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0389396537591697</v>
+        <v>0.1104299408634938</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6965</v>
+        <v>6994</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>254.6934930874957</v>
+        <v>257.8591544354101</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>35.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>38.59111203845274</v>
+        <v>36.48650661036867</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>35.63487833111565</v>
+        <v>29.93073683396423</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.033658137705005</v>
+        <v>0.8638746602072428</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0547849191979017</v>
+        <v>0.4047730272110821</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7839</v>
+        <v>7780</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>246.2969498818454</v>
+        <v>256.7290493113802</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>44.5</v>
+        <v>16.75</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>42.38642075086977</v>
+        <v>43.77219352727872</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>29.96194461046545</v>
+        <v>21.53860205650573</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.8886839978560498</v>
+        <v>0.9126483839864302</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0112094639565174</v>
+        <v>0.0573278190949545</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6910</v>
+        <v>7818</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>244.7027817018846</v>
+        <v>255.1513016246124</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>24.6</v>
+        <v>60.2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.47769477227117</v>
+        <v>28.75895228055232</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.79355673425065</v>
+        <v>19.99956133714834</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4535160247052854</v>
+        <v>1.117096110931922</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0797624252326234</v>
+        <v>-0.0389396536446757</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7770</v>
+        <v>6965</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>235.4780188893394</v>
+        <v>254.6934930874953</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>36.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.22352742265611</v>
+        <v>38.59111202097423</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>5.635051936054741</v>
+        <v>35.6348783372644</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>4.359469421529049</v>
+        <v>1.033658137705005</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.087920013682427</v>
+        <v>0.0547849192932908</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6862</v>
+        <v>7839</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>232.2619876365622</v>
+        <v>246.2969498818454</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>139.5</v>
+        <v>44.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.91711935692246</v>
+        <v>42.38642098649504</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.50090217789761</v>
+        <v>29.96194461046545</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.068736929043024</v>
+        <v>0.8886839978560498</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>1.451728813367822</v>
+        <v>-0.0112094641663828</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7760</v>
+        <v>6910</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>220.9501195739197</v>
+        <v>244.7027817018794</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>33</v>
+        <v>24.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>44.66426757379021</v>
+        <v>46.47769599736002</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>7.765228336577342</v>
+        <v>16.79355652548514</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.752158961936544</v>
+        <v>0.4535160247052854</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0349301358157093</v>
+        <v>0.0797624243645068</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7547</v>
+        <v>7705</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>218.4635725980818</v>
+        <v>237.4030980957353</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>50.7</v>
+        <v>30.1</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.93964446998825</v>
+        <v>41.88483337837825</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.08198475075697</v>
+        <v>19.98983468827038</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5747096707446395</v>
+        <v>0.9995602054026598</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1155486028380757</v>
+        <v>-0.0237546826550456</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6865</v>
+        <v>7770</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>216.0224372177213</v>
+        <v>235.4780188893394</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>26.7</v>
+        <v>36.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>54.33000543620424</v>
+        <v>49.22352745180388</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>11.04910077983422</v>
+        <v>5.635051936709991</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5185339441899208</v>
+        <v>4.359469421529049</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>1.232349671219098</v>
+        <v>0.08792001335807539</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7821</v>
+        <v>6862</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>211.4049835125538</v>
+        <v>232.2619876365621</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>39.1</v>
+        <v>139.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.48135410587293</v>
+        <v>43.91711936373772</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.27835526216628</v>
+        <v>15.50090219583272</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5690712396273394</v>
+        <v>1.068736929043024</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.052093931474262</v>
+        <v>1.451728812795426</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7791</v>
+        <v>7821</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>210.6411949296888</v>
+        <v>231.4049835125538</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>56.4</v>
+        <v>39.1</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>28.08886542230568</v>
+        <v>42.48135428509251</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>38.3809579599879</v>
+        <v>14.27835526216628</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.1279908783107467</v>
+        <v>0.5690712396273394</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0541099055627283</v>
+        <v>0.0520939312453109</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8032</v>
+        <v>7760</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>210.5611400251243</v>
+        <v>220.9501195739197</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>36.6</v>
+        <v>33</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.43425738546952</v>
+        <v>44.66426775202437</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.07469555799062</v>
+        <v>7.765228324161989</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.214205197952995</v>
+        <v>1.752158961936544</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.2047329222622258</v>
+        <v>0.0349301356535312</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6873</v>
+        <v>7547</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>209.7953118037626</v>
+        <v>218.463572598075</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>69</v>
+        <v>50.7</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>36.97420160859984</v>
+        <v>43.93964495008238</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>25.09398164381133</v>
+        <v>13.0819847334049</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.174925929434985</v>
+        <v>0.5747096707446395</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.2853638956234317</v>
+        <v>-0.1155486034104609</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7753</v>
+        <v>7791</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>203.4565358261155</v>
+        <v>210.6411949296889</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>36.3</v>
+        <v>56.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>34.34607310364541</v>
+        <v>28.0888654145514</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>7.858166371535707</v>
+        <v>38.3809579599879</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>5.500267302710038</v>
+        <v>0.1279908783107467</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.051843960410663</v>
+        <v>0.0541099053337807</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7823</v>
+        <v>8032</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>199.3075973197414</v>
+        <v>210.5611400251242</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>36.6</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>47.27237499466226</v>
+        <v>48.43425754279784</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>22.80759653550959</v>
+        <v>20.07469562911663</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2201790789842405</v>
+        <v>0.214205197952995</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0961066396767405</v>
+        <v>0.2047329221095923</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6890</v>
+        <v>6873</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>195.2567099754814</v>
+        <v>209.7953118037625</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.14028475694198</v>
+        <v>36.97420181025581</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.47988129821253</v>
+        <v>25.09398154392184</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4516159768640829</v>
+        <v>1.174925929434985</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>1.462397232824074</v>
+        <v>0.285363895146455</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6958</v>
+        <v>7753</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>193.9855086204062</v>
+        <v>203.4565358261157</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>17.2</v>
+        <v>36.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.8349916804656</v>
+        <v>34.34607301280825</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.03322815825963</v>
+        <v>7.858166379072983</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.790316669284555</v>
+        <v>5.500267302710038</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0428207614738651</v>
+        <v>0.0518439605060561</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7732</v>
+        <v>7823</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>192.6269385726509</v>
+        <v>199.3075973197414</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>34.75</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>50.47445324963424</v>
+        <v>47.27237499466226</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>4.437270392014344</v>
+        <v>22.80759653550959</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1228572920409974</v>
+        <v>0.2201790789842405</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0294019316876263</v>
+        <v>-0.0961066396767405</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7827</v>
+        <v>6890</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>191.9967970554801</v>
+        <v>195.2567099754814</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>154.5</v>
+        <v>167</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.10615732782065</v>
+        <v>46.14028465905147</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>10.85933919062419</v>
+        <v>13.47988153113229</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.847451512662071</v>
+        <v>0.4516159768640829</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.028620582092049</v>
+        <v>1.462397235685982</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7803</v>
+        <v>6958</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>169.3676897429345</v>
+        <v>193.9855086204062</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>19.1</v>
+        <v>17.2</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>37.98081007351704</v>
+        <v>42.83499167327738</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.09891048948879</v>
+        <v>18.03322811739178</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.7180005300119253</v>
+        <v>0.790316669284555</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,11 +6612,11 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.07286087913907011</v>
+        <v>-0.0428207614738651</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>41.09562280081632</v>
+        <v>41.09562275213875</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>22.54281787236456</v>
+        <v>22.54281789013419</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.112206476729337</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.3570533452826483</v>
+        <v>0.3570533453494251</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>166.8342591275712</v>
+        <v>166.8342591275694</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>117</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>36.09336262158222</v>
+        <v>36.09336282403678</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.76082739730857</v>
+        <v>12.76082742819966</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>1.162487948226823</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.6931552838522161</v>
+        <v>-0.6931552848061844</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>44.88570688719699</v>
+        <v>44.8857069227134</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.53390247165916</v>
+        <v>17.53390247301253</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.9134683192509764</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.4557066373874616</v>
+        <v>0.4557066373302185</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>156.9092979944412</v>
+        <v>156.9092979944411</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>129.5</v>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>35.83835110380977</v>
+        <v>35.83835128349068</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.6422902282605</v>
+        <v>12.64229030503755</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.6782428989434909</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-1.226950392780285</v>
+        <v>-1.226950393161853</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.66766445172205</v>
+        <v>41.66766451133797</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>16.75942642282803</v>
+        <v>16.75942646813868</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>1.282373612041951</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>1.213244971853789</v>
+        <v>1.21324497109061</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.00388353261597</v>
+        <v>46.0038836232662</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.01003102484724</v>
+        <v>14.01003121220668</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.4983275865348299</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0257805195040258</v>
+        <v>-0.025780519790223</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>147.0415813690103</v>
+        <v>147.0415813690101</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>285</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>48.97230522805629</v>
+        <v>48.97230520172965</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.73046362492139</v>
+        <v>12.7304636299143</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.4793848142559423</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>1.729783056036148</v>
+        <v>1.729783056417693</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6899</v>
+        <v>6988</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>144.2611545666506</v>
+        <v>145.9644325877834</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.13866043078568</v>
+        <v>45.05227091869354</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>19.78513447161204</v>
+        <v>6.758821128192802</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.195893804185589</v>
+        <v>1.23187967729315</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.1951361570028285</v>
+        <v>-0.028282613808857</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7747</v>
+        <v>6899</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>135.6157293265727</v>
+        <v>144.2611545666506</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>113.5</v>
+        <v>50</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>52.04290070821912</v>
+        <v>39.13866052978701</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>9.071672819754264</v>
+        <v>19.78513457213514</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.16157293265727</v>
+        <v>1.195893804185589</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>3.573671582715771</v>
+        <v>0.1951361568883578</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6925</v>
+        <v>7747</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>131.7396239560941</v>
+        <v>135.6157293265727</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>49.6</v>
+        <v>113.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>35.31995098668546</v>
+        <v>52.04290071417858</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>13.49576772098834</v>
+        <v>9.071672798457632</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.189569594295435</v>
+        <v>0.16157293265727</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.1154082605575679</v>
+        <v>3.573671582620372</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>7705</v>
+        <v>7732</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>127.4030980957353</v>
+        <v>132.6269385726509</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>30.1</v>
+        <v>34.75</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>41.88483318910941</v>
+        <v>50.47445091087331</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.98983468677884</v>
+        <v>4.437269946418552</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.9995602054026598</v>
+        <v>0.1228572920409974</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0237546825596448</v>
+        <v>-0.0294019240558499</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>6869</v>
+        <v>6925</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>77.44265665453494</v>
+        <v>131.7396239560941</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>46.39896317021369</v>
+        <v>35.31995006844055</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>16.13674961394444</v>
+        <v>13.49576801681214</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5114338124820856</v>
+        <v>1.189569594295435</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.297449142967788</v>
+        <v>0.1154082618931344</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>6988</v>
+        <v>6869</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>70.96443258778335</v>
+        <v>77.44265665453496</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>11.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>45.05227268802442</v>
+        <v>46.39896342083989</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>6.758821125412332</v>
+        <v>16.1367495102538</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.23187967729315</v>
+        <v>0.5114338124820856</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0282826138565555</v>
+        <v>0.2974491423954104</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
